--- a/sandbox/MassLossInvestigation/SamplesTested.xlsx
+++ b/sandbox/MassLossInvestigation/SamplesTested.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://millfieldgroup-my.sharepoint.com/personal/thomas-dodd_millfield-group_co_uk/Documents/Cambridge/PhD/writing/papers/UoC_Paper1/sandbox/MassLossInvestigation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{4314D998-4C24-8F4B-A050-CA8877770391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EF6E843-F580-6B46-B80A-2CFF44DEB520}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{4314D998-4C24-8F4B-A050-CA8877770391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FF36430-56F6-AF43-8880-2D1B793AB527}"/>
   <bookViews>
-    <workbookView xWindow="-23040" yWindow="-7000" windowWidth="23040" windowHeight="40360" xr2:uid="{6CD22F8F-775D-C548-B021-D508480430FF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{6CD22F8F-775D-C548-B021-D508480430FF}"/>
   </bookViews>
   <sheets>
     <sheet name="90oC" sheetId="1" r:id="rId1"/>
@@ -63,13 +63,13 @@
     <t>Cure Mass Loss (%)</t>
   </si>
   <si>
-    <t>Networked Extent (g)</t>
-  </si>
-  <si>
     <t>n/a</t>
   </si>
   <si>
     <t>For samples 1 and 5: Specimen disintegrated during tetrahydrofuran exposure and the dispersed insoluble material could not be quantitatively recovered.</t>
+  </si>
+  <si>
+    <t>THF-Insoluble Fraction (%)</t>
   </si>
 </sst>
 </file>
@@ -2609,7 +2609,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
@@ -2720,7 +2720,7 @@
         <v>6.7929936106434994</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="2" t="e">
         <f>(G6/D6)*100</f>
@@ -2749,7 +2749,7 @@
         <v>10.126909290535076</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2" t="e">
         <f>(G7/D7)*100</f>
@@ -2758,11 +2758,12 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2795,7 +2796,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
